--- a/FILES/INPUTS/DICCIONARIO_TICKERS.xlsx
+++ b/FILES/INPUTS/DICCIONARIO_TICKERS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\landa\OneDrive\Escritorio\R_Para_Las_Finanzas_Rodrigo_Escobar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\landa\OneDrive\Escritorio\R_Para_Las_Finanzas_Rodrigo_Escobar\FILES\INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7CD232-6B67-485F-9D52-58FFCCE37134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523B2C8D-1666-4B77-8C57-49AC32223625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{C769B749-9B38-4F61-8013-263B4B02318E}"/>
+    <workbookView xWindow="9732" yWindow="2508" windowWidth="8256" windowHeight="8448" xr2:uid="{C769B749-9B38-4F61-8013-263B4B02318E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -4514,7 +4514,7 @@
     <t>LOCAL</t>
   </si>
   <si>
-    <t>EXTANJERA</t>
+    <t>EXTRANJERA</t>
   </si>
 </sst>
 </file>

--- a/FILES/INPUTS/DICCIONARIO_TICKERS.xlsx
+++ b/FILES/INPUTS/DICCIONARIO_TICKERS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\landa\OneDrive\Escritorio\R_Para_Las_Finanzas_Rodrigo_Escobar\FILES\INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523B2C8D-1666-4B77-8C57-49AC32223625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884CFA4C-6A13-46C6-90A2-09522A602B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9732" yWindow="2508" windowWidth="8256" windowHeight="8448" xr2:uid="{C769B749-9B38-4F61-8013-263B4B02318E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C769B749-9B38-4F61-8013-263B4B02318E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$498</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$496</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1486">
   <si>
     <t>ID_EMPRESA</t>
   </si>
@@ -1196,9 +1196,6 @@
     <t>EXT250</t>
   </si>
   <si>
-    <t>EXT251</t>
-  </si>
-  <si>
     <t>EXT252</t>
   </si>
   <si>
@@ -1256,9 +1253,6 @@
     <t>EXT270</t>
   </si>
   <si>
-    <t>EXT271</t>
-  </si>
-  <si>
     <t>EXT272</t>
   </si>
   <si>
@@ -3224,12 +3218,6 @@
     <t>State Street</t>
   </si>
   <si>
-    <t>MMC</t>
-  </si>
-  <si>
-    <t>Marsh McLennan</t>
-  </si>
-  <si>
     <t>CME</t>
   </si>
   <si>
@@ -3342,12 +3330,6 @@
   </si>
   <si>
     <t>W.R. Berkley</t>
-  </si>
-  <si>
-    <t>CMA</t>
-  </si>
-  <si>
-    <t>Comerica</t>
   </si>
   <si>
     <t>A</t>
@@ -4887,7 +4869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5405E5E4-8AD8-41E7-B4EE-E3800A1407B4}">
-  <dimension ref="A1:D498"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
@@ -4901,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="C1" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="D1" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -4918,10 +4900,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
       <c r="D2" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -4932,10 +4914,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="D3" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -4946,10 +4928,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="D4" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -4960,10 +4942,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
       <c r="D5" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -4974,10 +4956,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="D6" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -4988,10 +4970,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="D7" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -5002,10 +4984,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="D8" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -5016,10 +4998,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
       <c r="D9" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -5030,10 +5012,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="D10" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -5044,10 +5026,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="D11" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -5058,10 +5040,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="D12" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -5072,10 +5054,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1433</v>
+        <v>1427</v>
       </c>
       <c r="D13" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -5086,10 +5068,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="D14" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -5100,10 +5082,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="D15" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -5114,10 +5096,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="D16" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -5128,10 +5110,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="D17" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -5142,10 +5124,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="D18" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -5156,10 +5138,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="D19" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -5170,10 +5152,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="D20" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -5184,10 +5166,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="D21" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -5198,10 +5180,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="D22" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -5212,10 +5194,10 @@
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="D23" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -5226,10 +5208,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="D24" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -5240,10 +5222,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="D25" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -5254,10 +5236,10 @@
         <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="D26" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -5268,10 +5250,10 @@
         <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="D27" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -5282,10 +5264,10 @@
         <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="D28" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -5296,10 +5278,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="D29" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -5310,10 +5292,10 @@
         <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="D30" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -5324,10 +5306,10 @@
         <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="D31" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -5338,10 +5320,10 @@
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
       <c r="D32" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -5352,10 +5334,10 @@
         <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
       <c r="D33" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -5366,10 +5348,10 @@
         <v>33</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="D34" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -5380,10 +5362,10 @@
         <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="D35" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -5394,10 +5376,10 @@
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1456</v>
+        <v>1450</v>
       </c>
       <c r="D36" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -5408,10 +5390,10 @@
         <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="D37" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -5422,10 +5404,10 @@
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="D38" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -5436,10 +5418,10 @@
         <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="D39" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -5450,10 +5432,10 @@
         <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D40" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -5464,10 +5446,10 @@
         <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="D41" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -5478,10 +5460,10 @@
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="D42" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -5492,10 +5474,10 @@
         <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="D43" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -5506,10 +5488,10 @@
         <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="D44" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -5520,10 +5502,10 @@
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="D45" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -5534,10 +5516,10 @@
         <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="D46" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -5548,10 +5530,10 @@
         <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="D47" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -5562,10 +5544,10 @@
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="D48" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -5576,10 +5558,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="D49" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -5590,10 +5572,10 @@
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="D50" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -5604,10 +5586,10 @@
         <v>50</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="D51" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -5618,10 +5600,10 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="D52" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -5632,10 +5614,10 @@
         <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="D53" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -5646,10 +5628,10 @@
         <v>53</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="D54" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -5660,10 +5642,10 @@
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="D55" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -5674,10 +5656,10 @@
         <v>55</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="D56" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -5688,10 +5670,10 @@
         <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="D57" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -5702,10 +5684,10 @@
         <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="D58" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -5716,10 +5698,10 @@
         <v>58</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="D59" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -5730,10 +5712,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="D60" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -5744,10 +5726,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="D61" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -5758,10 +5740,10 @@
         <v>61</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="D62" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -5772,10 +5754,10 @@
         <v>62</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="D63" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -5786,10 +5768,10 @@
         <v>63</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D64" t="s">
         <v>1484</v>
-      </c>
-      <c r="D64" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -5800,10 +5782,10 @@
         <v>64</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="D65" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -5814,10 +5796,10 @@
         <v>65</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="D66" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -5828,10 +5810,10 @@
         <v>66</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="D67" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -5842,10 +5824,10 @@
         <v>67</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="D68" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -5853,13 +5835,13 @@
         <v>135</v>
       </c>
       <c r="B69" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C69" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D69" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -5867,13 +5849,13 @@
         <v>136</v>
       </c>
       <c r="B70" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C70" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D70" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -5881,13 +5863,13 @@
         <v>137</v>
       </c>
       <c r="B71" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C71" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D71" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -5895,13 +5877,13 @@
         <v>138</v>
       </c>
       <c r="B72" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C72" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D72" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -5909,13 +5891,13 @@
         <v>139</v>
       </c>
       <c r="B73" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C73" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D73" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -5923,13 +5905,13 @@
         <v>140</v>
       </c>
       <c r="B74" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C74" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D74" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -5937,13 +5919,13 @@
         <v>141</v>
       </c>
       <c r="B75" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C75" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D75" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -5951,13 +5933,13 @@
         <v>142</v>
       </c>
       <c r="B76" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C76" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D76" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -5965,13 +5947,13 @@
         <v>143</v>
       </c>
       <c r="B77" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C77" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D77" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -5979,13 +5961,13 @@
         <v>144</v>
       </c>
       <c r="B78" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C78" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D78" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -5993,13 +5975,13 @@
         <v>145</v>
       </c>
       <c r="B79" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C79" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D79" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -6007,13 +5989,13 @@
         <v>146</v>
       </c>
       <c r="B80" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C80" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D80" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -6021,13 +6003,13 @@
         <v>147</v>
       </c>
       <c r="B81" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C81" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D81" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -6035,13 +6017,13 @@
         <v>148</v>
       </c>
       <c r="B82" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C82" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D82" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -6049,13 +6031,13 @@
         <v>149</v>
       </c>
       <c r="B83" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C83" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D83" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -6063,13 +6045,13 @@
         <v>150</v>
       </c>
       <c r="B84" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C84" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D84" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -6077,13 +6059,13 @@
         <v>151</v>
       </c>
       <c r="B85" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C85" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D85" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -6091,13 +6073,13 @@
         <v>152</v>
       </c>
       <c r="B86" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C86" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D86" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -6105,13 +6087,13 @@
         <v>153</v>
       </c>
       <c r="B87" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C87" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D87" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -6119,13 +6101,13 @@
         <v>154</v>
       </c>
       <c r="B88" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C88" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D88" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -6133,13 +6115,13 @@
         <v>155</v>
       </c>
       <c r="B89" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C89" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D89" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -6147,13 +6129,13 @@
         <v>156</v>
       </c>
       <c r="B90" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C90" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D90" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -6161,13 +6143,13 @@
         <v>157</v>
       </c>
       <c r="B91" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C91" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D91" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -6175,13 +6157,13 @@
         <v>158</v>
       </c>
       <c r="B92" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C92" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D92" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -6189,13 +6171,13 @@
         <v>159</v>
       </c>
       <c r="B93" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C93" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D93" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -6203,13 +6185,13 @@
         <v>160</v>
       </c>
       <c r="B94" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C94" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D94" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -6217,13 +6199,13 @@
         <v>161</v>
       </c>
       <c r="B95" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C95" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D95" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -6231,13 +6213,13 @@
         <v>162</v>
       </c>
       <c r="B96" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C96" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D96" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -6245,13 +6227,13 @@
         <v>163</v>
       </c>
       <c r="B97" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C97" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D97" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -6259,13 +6241,13 @@
         <v>164</v>
       </c>
       <c r="B98" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C98" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D98" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -6273,13 +6255,13 @@
         <v>165</v>
       </c>
       <c r="B99" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C99" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D99" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -6287,13 +6269,13 @@
         <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C100" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D100" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -6301,13 +6283,13 @@
         <v>167</v>
       </c>
       <c r="B101" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C101" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D101" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -6315,13 +6297,13 @@
         <v>168</v>
       </c>
       <c r="B102" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C102" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D102" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -6329,13 +6311,13 @@
         <v>169</v>
       </c>
       <c r="B103" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C103" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D103" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -6343,13 +6325,13 @@
         <v>170</v>
       </c>
       <c r="B104" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C104" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D104" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -6357,13 +6339,13 @@
         <v>171</v>
       </c>
       <c r="B105" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C105" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D105" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -6371,13 +6353,13 @@
         <v>172</v>
       </c>
       <c r="B106" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C106" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D106" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -6385,13 +6367,13 @@
         <v>173</v>
       </c>
       <c r="B107" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C107" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D107" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -6399,13 +6381,13 @@
         <v>174</v>
       </c>
       <c r="B108" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C108" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D108" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -6413,13 +6395,13 @@
         <v>175</v>
       </c>
       <c r="B109" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C109" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D109" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -6427,13 +6409,13 @@
         <v>176</v>
       </c>
       <c r="B110" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C110" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D110" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -6441,13 +6423,13 @@
         <v>177</v>
       </c>
       <c r="B111" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C111" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D111" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -6455,13 +6437,13 @@
         <v>178</v>
       </c>
       <c r="B112" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C112" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D112" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -6469,13 +6451,13 @@
         <v>179</v>
       </c>
       <c r="B113" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C113" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D113" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -6483,13 +6465,13 @@
         <v>180</v>
       </c>
       <c r="B114" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C114" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D114" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -6497,13 +6479,13 @@
         <v>181</v>
       </c>
       <c r="B115" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C115" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D115" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -6511,13 +6493,13 @@
         <v>182</v>
       </c>
       <c r="B116" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C116" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D116" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -6525,13 +6507,13 @@
         <v>183</v>
       </c>
       <c r="B117" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C117" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D117" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -6539,13 +6521,13 @@
         <v>184</v>
       </c>
       <c r="B118" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C118" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D118" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -6553,13 +6535,13 @@
         <v>185</v>
       </c>
       <c r="B119" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C119" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D119" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -6567,13 +6549,13 @@
         <v>186</v>
       </c>
       <c r="B120" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C120" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D120" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -6581,13 +6563,13 @@
         <v>187</v>
       </c>
       <c r="B121" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C121" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D121" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -6595,13 +6577,13 @@
         <v>188</v>
       </c>
       <c r="B122" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C122" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D122" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -6609,13 +6591,13 @@
         <v>189</v>
       </c>
       <c r="B123" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C123" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D123" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -6623,13 +6605,13 @@
         <v>190</v>
       </c>
       <c r="B124" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C124" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D124" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -6637,13 +6619,13 @@
         <v>191</v>
       </c>
       <c r="B125" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C125" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D125" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -6651,13 +6633,13 @@
         <v>192</v>
       </c>
       <c r="B126" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C126" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D126" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -6665,13 +6647,13 @@
         <v>193</v>
       </c>
       <c r="B127" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C127" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D127" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -6679,13 +6661,13 @@
         <v>194</v>
       </c>
       <c r="B128" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C128" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D128" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -6693,13 +6675,13 @@
         <v>195</v>
       </c>
       <c r="B129" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C129" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D129" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -6707,13 +6689,13 @@
         <v>196</v>
       </c>
       <c r="B130" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C130" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D130" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -6721,13 +6703,13 @@
         <v>197</v>
       </c>
       <c r="B131" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C131" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D131" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -6735,13 +6717,13 @@
         <v>198</v>
       </c>
       <c r="B132" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C132" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D132" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -6749,13 +6731,13 @@
         <v>199</v>
       </c>
       <c r="B133" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C133" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D133" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -6763,13 +6745,13 @@
         <v>200</v>
       </c>
       <c r="B134" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C134" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D134" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -6777,13 +6759,13 @@
         <v>201</v>
       </c>
       <c r="B135" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C135" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D135" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -6791,13 +6773,13 @@
         <v>202</v>
       </c>
       <c r="B136" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C136" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D136" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -6805,13 +6787,13 @@
         <v>203</v>
       </c>
       <c r="B137" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C137" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D137" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -6819,13 +6801,13 @@
         <v>204</v>
       </c>
       <c r="B138" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C138" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D138" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -6833,13 +6815,13 @@
         <v>205</v>
       </c>
       <c r="B139" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C139" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D139" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -6847,13 +6829,13 @@
         <v>206</v>
       </c>
       <c r="B140" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C140" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D140" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -6861,13 +6843,13 @@
         <v>207</v>
       </c>
       <c r="B141" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C141" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D141" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -6875,13 +6857,13 @@
         <v>208</v>
       </c>
       <c r="B142" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C142" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D142" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -6889,13 +6871,13 @@
         <v>209</v>
       </c>
       <c r="B143" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C143" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D143" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -6903,13 +6885,13 @@
         <v>210</v>
       </c>
       <c r="B144" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C144" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D144" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -6917,13 +6899,13 @@
         <v>211</v>
       </c>
       <c r="B145" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C145" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D145" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -6931,13 +6913,13 @@
         <v>212</v>
       </c>
       <c r="B146" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C146" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D146" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -6945,13 +6927,13 @@
         <v>213</v>
       </c>
       <c r="B147" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C147" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D147" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -6959,13 +6941,13 @@
         <v>214</v>
       </c>
       <c r="B148" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C148" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D148" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -6973,13 +6955,13 @@
         <v>215</v>
       </c>
       <c r="B149" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C149" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D149" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -6987,13 +6969,13 @@
         <v>216</v>
       </c>
       <c r="B150" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C150" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D150" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -7001,13 +6983,13 @@
         <v>217</v>
       </c>
       <c r="B151" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C151" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D151" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -7015,13 +6997,13 @@
         <v>218</v>
       </c>
       <c r="B152" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C152" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D152" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -7029,13 +7011,13 @@
         <v>219</v>
       </c>
       <c r="B153" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C153" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D153" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -7043,13 +7025,13 @@
         <v>220</v>
       </c>
       <c r="B154" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C154" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D154" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -7057,13 +7039,13 @@
         <v>221</v>
       </c>
       <c r="B155" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C155" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D155" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -7071,13 +7053,13 @@
         <v>222</v>
       </c>
       <c r="B156" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C156" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D156" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -7085,13 +7067,13 @@
         <v>223</v>
       </c>
       <c r="B157" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C157" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D157" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -7099,13 +7081,13 @@
         <v>224</v>
       </c>
       <c r="B158" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C158" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D158" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -7113,13 +7095,13 @@
         <v>225</v>
       </c>
       <c r="B159" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C159" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D159" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -7127,13 +7109,13 @@
         <v>226</v>
       </c>
       <c r="B160" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C160" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D160" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -7141,13 +7123,13 @@
         <v>227</v>
       </c>
       <c r="B161" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C161" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D161" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -7155,13 +7137,13 @@
         <v>228</v>
       </c>
       <c r="B162" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C162" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D162" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -7169,13 +7151,13 @@
         <v>229</v>
       </c>
       <c r="B163" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C163" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D163" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -7183,13 +7165,13 @@
         <v>230</v>
       </c>
       <c r="B164" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C164" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D164" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
@@ -7197,13 +7179,13 @@
         <v>231</v>
       </c>
       <c r="B165" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C165" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D165" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -7211,13 +7193,13 @@
         <v>232</v>
       </c>
       <c r="B166" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C166" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D166" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -7225,13 +7207,13 @@
         <v>233</v>
       </c>
       <c r="B167" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C167" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D167" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -7239,13 +7221,13 @@
         <v>234</v>
       </c>
       <c r="B168" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C168" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D168" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -7253,13 +7235,13 @@
         <v>235</v>
       </c>
       <c r="B169" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C169" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D169" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -7267,13 +7249,13 @@
         <v>236</v>
       </c>
       <c r="B170" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C170" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D170" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -7281,13 +7263,13 @@
         <v>237</v>
       </c>
       <c r="B171" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C171" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D171" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -7295,13 +7277,13 @@
         <v>238</v>
       </c>
       <c r="B172" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C172" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D172" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -7309,13 +7291,13 @@
         <v>239</v>
       </c>
       <c r="B173" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C173" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D173" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
@@ -7323,13 +7305,13 @@
         <v>240</v>
       </c>
       <c r="B174" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C174" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D174" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
@@ -7337,13 +7319,13 @@
         <v>241</v>
       </c>
       <c r="B175" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C175" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D175" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -7351,13 +7333,13 @@
         <v>242</v>
       </c>
       <c r="B176" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C176" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D176" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
@@ -7365,13 +7347,13 @@
         <v>243</v>
       </c>
       <c r="B177" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C177" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D177" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
@@ -7379,13 +7361,13 @@
         <v>244</v>
       </c>
       <c r="B178" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C178" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D178" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -7393,13 +7375,13 @@
         <v>245</v>
       </c>
       <c r="B179" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C179" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D179" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -7407,13 +7389,13 @@
         <v>246</v>
       </c>
       <c r="B180" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C180" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D180" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -7421,13 +7403,13 @@
         <v>247</v>
       </c>
       <c r="B181" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C181" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D181" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -7435,13 +7417,13 @@
         <v>248</v>
       </c>
       <c r="B182" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C182" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D182" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -7449,13 +7431,13 @@
         <v>249</v>
       </c>
       <c r="B183" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C183" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D183" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -7463,13 +7445,13 @@
         <v>250</v>
       </c>
       <c r="B184" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C184" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D184" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -7477,13 +7459,13 @@
         <v>251</v>
       </c>
       <c r="B185" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C185" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D185" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -7491,13 +7473,13 @@
         <v>252</v>
       </c>
       <c r="B186" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C186" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D186" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -7505,13 +7487,13 @@
         <v>253</v>
       </c>
       <c r="B187" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C187" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D187" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -7519,13 +7501,13 @@
         <v>254</v>
       </c>
       <c r="B188" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C188" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D188" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -7533,13 +7515,13 @@
         <v>255</v>
       </c>
       <c r="B189" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C189" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D189" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -7547,13 +7529,13 @@
         <v>256</v>
       </c>
       <c r="B190" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C190" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D190" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -7561,13 +7543,13 @@
         <v>257</v>
       </c>
       <c r="B191" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C191" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D191" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -7575,13 +7557,13 @@
         <v>258</v>
       </c>
       <c r="B192" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C192" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D192" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -7589,13 +7571,13 @@
         <v>259</v>
       </c>
       <c r="B193" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C193" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D193" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
@@ -7603,13 +7585,13 @@
         <v>260</v>
       </c>
       <c r="B194" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C194" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D194" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -7617,13 +7599,13 @@
         <v>261</v>
       </c>
       <c r="B195" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C195" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D195" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -7631,13 +7613,13 @@
         <v>262</v>
       </c>
       <c r="B196" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C196" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D196" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -7645,13 +7627,13 @@
         <v>263</v>
       </c>
       <c r="B197" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C197" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D197" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -7659,13 +7641,13 @@
         <v>264</v>
       </c>
       <c r="B198" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C198" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D198" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -7673,13 +7655,13 @@
         <v>265</v>
       </c>
       <c r="B199" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C199" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D199" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
@@ -7687,13 +7669,13 @@
         <v>266</v>
       </c>
       <c r="B200" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C200" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D200" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -7701,13 +7683,13 @@
         <v>267</v>
       </c>
       <c r="B201" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C201" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D201" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -7715,13 +7697,13 @@
         <v>268</v>
       </c>
       <c r="B202" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C202" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D202" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -7729,13 +7711,13 @@
         <v>269</v>
       </c>
       <c r="B203" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C203" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D203" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -7743,13 +7725,13 @@
         <v>270</v>
       </c>
       <c r="B204" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C204" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D204" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
@@ -7757,13 +7739,13 @@
         <v>271</v>
       </c>
       <c r="B205" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C205" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D205" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
@@ -7771,13 +7753,13 @@
         <v>272</v>
       </c>
       <c r="B206" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C206" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D206" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -7785,13 +7767,13 @@
         <v>273</v>
       </c>
       <c r="B207" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C207" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D207" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -7799,13 +7781,13 @@
         <v>274</v>
       </c>
       <c r="B208" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C208" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D208" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -7813,13 +7795,13 @@
         <v>275</v>
       </c>
       <c r="B209" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C209" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D209" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -7827,13 +7809,13 @@
         <v>276</v>
       </c>
       <c r="B210" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C210" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D210" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -7841,13 +7823,13 @@
         <v>277</v>
       </c>
       <c r="B211" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C211" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D211" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
@@ -7855,13 +7837,13 @@
         <v>278</v>
       </c>
       <c r="B212" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C212" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D212" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
@@ -7869,13 +7851,13 @@
         <v>279</v>
       </c>
       <c r="B213" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C213" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D213" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -7883,13 +7865,13 @@
         <v>280</v>
       </c>
       <c r="B214" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C214" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D214" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -7897,13 +7879,13 @@
         <v>281</v>
       </c>
       <c r="B215" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C215" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D215" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
@@ -7911,13 +7893,13 @@
         <v>282</v>
       </c>
       <c r="B216" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C216" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D216" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -7925,13 +7907,13 @@
         <v>283</v>
       </c>
       <c r="B217" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C217" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D217" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
@@ -7939,13 +7921,13 @@
         <v>284</v>
       </c>
       <c r="B218" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C218" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D218" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -7953,13 +7935,13 @@
         <v>285</v>
       </c>
       <c r="B219" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C219" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D219" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -7967,13 +7949,13 @@
         <v>286</v>
       </c>
       <c r="B220" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C220" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D220" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
@@ -7981,13 +7963,13 @@
         <v>287</v>
       </c>
       <c r="B221" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C221" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D221" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -7995,13 +7977,13 @@
         <v>288</v>
       </c>
       <c r="B222" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C222" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D222" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
@@ -8009,13 +7991,13 @@
         <v>289</v>
       </c>
       <c r="B223" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C223" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D223" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
@@ -8023,13 +8005,13 @@
         <v>290</v>
       </c>
       <c r="B224" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C224" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D224" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
@@ -8037,13 +8019,13 @@
         <v>291</v>
       </c>
       <c r="B225" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C225" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D225" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
@@ -8051,13 +8033,13 @@
         <v>292</v>
       </c>
       <c r="B226" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C226" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D226" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
@@ -8065,13 +8047,13 @@
         <v>293</v>
       </c>
       <c r="B227" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C227" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D227" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -8079,13 +8061,13 @@
         <v>294</v>
       </c>
       <c r="B228" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C228" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D228" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
@@ -8093,13 +8075,13 @@
         <v>295</v>
       </c>
       <c r="B229" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C229" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D229" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
@@ -8107,13 +8089,13 @@
         <v>296</v>
       </c>
       <c r="B230" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C230" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D230" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
@@ -8121,13 +8103,13 @@
         <v>297</v>
       </c>
       <c r="B231" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C231" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D231" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
@@ -8135,13 +8117,13 @@
         <v>298</v>
       </c>
       <c r="B232" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C232" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D232" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
@@ -8149,13 +8131,13 @@
         <v>299</v>
       </c>
       <c r="B233" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C233" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D233" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
@@ -8163,13 +8145,13 @@
         <v>300</v>
       </c>
       <c r="B234" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C234" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D234" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
@@ -8177,13 +8159,13 @@
         <v>301</v>
       </c>
       <c r="B235" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C235" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D235" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
@@ -8191,13 +8173,13 @@
         <v>302</v>
       </c>
       <c r="B236" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C236" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D236" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
@@ -8205,13 +8187,13 @@
         <v>303</v>
       </c>
       <c r="B237" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C237" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D237" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
@@ -8219,13 +8201,13 @@
         <v>304</v>
       </c>
       <c r="B238" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C238" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D238" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -8233,13 +8215,13 @@
         <v>305</v>
       </c>
       <c r="B239" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C239" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D239" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
@@ -8247,13 +8229,13 @@
         <v>306</v>
       </c>
       <c r="B240" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C240" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D240" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
@@ -8261,13 +8243,13 @@
         <v>307</v>
       </c>
       <c r="B241" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C241" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D241" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -8275,13 +8257,13 @@
         <v>308</v>
       </c>
       <c r="B242" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C242" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D242" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -8289,13 +8271,13 @@
         <v>309</v>
       </c>
       <c r="B243" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C243" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D243" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
@@ -8303,13 +8285,13 @@
         <v>310</v>
       </c>
       <c r="B244" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C244" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D244" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
@@ -8317,13 +8299,13 @@
         <v>311</v>
       </c>
       <c r="B245" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C245" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D245" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -8331,13 +8313,13 @@
         <v>312</v>
       </c>
       <c r="B246" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C246" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D246" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -8345,13 +8327,13 @@
         <v>313</v>
       </c>
       <c r="B247" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C247" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D247" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
@@ -8359,13 +8341,13 @@
         <v>314</v>
       </c>
       <c r="B248" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C248" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D248" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
@@ -8373,13 +8355,13 @@
         <v>315</v>
       </c>
       <c r="B249" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C249" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D249" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
@@ -8387,13 +8369,13 @@
         <v>316</v>
       </c>
       <c r="B250" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C250" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D250" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -8401,13 +8383,13 @@
         <v>317</v>
       </c>
       <c r="B251" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C251" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D251" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
@@ -8415,13 +8397,13 @@
         <v>318</v>
       </c>
       <c r="B252" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C252" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D252" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -8429,13 +8411,13 @@
         <v>319</v>
       </c>
       <c r="B253" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C253" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D253" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
@@ -8443,13 +8425,13 @@
         <v>320</v>
       </c>
       <c r="B254" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C254" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D254" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
@@ -8457,13 +8439,13 @@
         <v>321</v>
       </c>
       <c r="B255" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C255" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D255" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
@@ -8471,13 +8453,13 @@
         <v>322</v>
       </c>
       <c r="B256" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C256" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D256" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -8485,13 +8467,13 @@
         <v>323</v>
       </c>
       <c r="B257" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C257" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D257" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -8499,13 +8481,13 @@
         <v>324</v>
       </c>
       <c r="B258" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C258" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D258" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
@@ -8513,13 +8495,13 @@
         <v>325</v>
       </c>
       <c r="B259" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C259" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D259" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
@@ -8527,13 +8509,13 @@
         <v>326</v>
       </c>
       <c r="B260" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C260" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D260" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
@@ -8541,13 +8523,13 @@
         <v>327</v>
       </c>
       <c r="B261" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C261" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D261" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
@@ -8555,13 +8537,13 @@
         <v>328</v>
       </c>
       <c r="B262" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C262" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D262" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
@@ -8569,13 +8551,13 @@
         <v>329</v>
       </c>
       <c r="B263" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C263" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D263" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
@@ -8583,13 +8565,13 @@
         <v>330</v>
       </c>
       <c r="B264" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C264" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="D264" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -8597,13 +8579,13 @@
         <v>331</v>
       </c>
       <c r="B265" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C265" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D265" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
@@ -8611,13 +8593,13 @@
         <v>332</v>
       </c>
       <c r="B266" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C266" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D266" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
@@ -8625,13 +8607,13 @@
         <v>333</v>
       </c>
       <c r="B267" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C267" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="D267" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
@@ -8639,13 +8621,13 @@
         <v>334</v>
       </c>
       <c r="B268" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C268" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D268" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
@@ -8653,13 +8635,13 @@
         <v>335</v>
       </c>
       <c r="B269" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C269" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="D269" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
@@ -8667,13 +8649,13 @@
         <v>336</v>
       </c>
       <c r="B270" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C270" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D270" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
@@ -8681,13 +8663,13 @@
         <v>337</v>
       </c>
       <c r="B271" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C271" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="D271" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
@@ -8695,13 +8677,13 @@
         <v>338</v>
       </c>
       <c r="B272" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C272" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D272" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
@@ -8709,13 +8691,13 @@
         <v>339</v>
       </c>
       <c r="B273" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C273" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D273" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
@@ -8723,13 +8705,13 @@
         <v>340</v>
       </c>
       <c r="B274" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C274" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D274" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
@@ -8737,13 +8719,13 @@
         <v>341</v>
       </c>
       <c r="B275" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C275" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D275" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
@@ -8751,13 +8733,13 @@
         <v>342</v>
       </c>
       <c r="B276" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C276" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D276" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
@@ -8765,13 +8747,13 @@
         <v>343</v>
       </c>
       <c r="B277" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C277" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D277" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
@@ -8779,13 +8761,13 @@
         <v>344</v>
       </c>
       <c r="B278" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C278" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D278" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
@@ -8793,13 +8775,13 @@
         <v>345</v>
       </c>
       <c r="B279" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C279" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D279" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
@@ -8807,13 +8789,13 @@
         <v>346</v>
       </c>
       <c r="B280" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C280" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="D280" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
@@ -8821,13 +8803,13 @@
         <v>347</v>
       </c>
       <c r="B281" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C281" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D281" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
@@ -8835,13 +8817,13 @@
         <v>348</v>
       </c>
       <c r="B282" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C282" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D282" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
@@ -8849,13 +8831,13 @@
         <v>349</v>
       </c>
       <c r="B283" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C283" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D283" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
@@ -8863,13 +8845,13 @@
         <v>350</v>
       </c>
       <c r="B284" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C284" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D284" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
@@ -8877,13 +8859,13 @@
         <v>351</v>
       </c>
       <c r="B285" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C285" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D285" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
@@ -8891,13 +8873,13 @@
         <v>352</v>
       </c>
       <c r="B286" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C286" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D286" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -8905,13 +8887,13 @@
         <v>353</v>
       </c>
       <c r="B287" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C287" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D287" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -8919,13 +8901,13 @@
         <v>354</v>
       </c>
       <c r="B288" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C288" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D288" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -8933,13 +8915,13 @@
         <v>355</v>
       </c>
       <c r="B289" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C289" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D289" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -8947,13 +8929,13 @@
         <v>356</v>
       </c>
       <c r="B290" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C290" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D290" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -8961,13 +8943,13 @@
         <v>357</v>
       </c>
       <c r="B291" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C291" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D291" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -8975,13 +8957,13 @@
         <v>358</v>
       </c>
       <c r="B292" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C292" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D292" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -8989,13 +8971,13 @@
         <v>359</v>
       </c>
       <c r="B293" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C293" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D293" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
@@ -9003,13 +8985,13 @@
         <v>360</v>
       </c>
       <c r="B294" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C294" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D294" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
@@ -9017,13 +8999,13 @@
         <v>361</v>
       </c>
       <c r="B295" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C295" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D295" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
@@ -9031,13 +9013,13 @@
         <v>362</v>
       </c>
       <c r="B296" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C296" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D296" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
@@ -9045,13 +9027,13 @@
         <v>363</v>
       </c>
       <c r="B297" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C297" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D297" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
@@ -9059,13 +9041,13 @@
         <v>364</v>
       </c>
       <c r="B298" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C298" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="D298" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
@@ -9073,13 +9055,13 @@
         <v>365</v>
       </c>
       <c r="B299" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C299" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="D299" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -9087,13 +9069,13 @@
         <v>366</v>
       </c>
       <c r="B300" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C300" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D300" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
@@ -9101,13 +9083,13 @@
         <v>367</v>
       </c>
       <c r="B301" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C301" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D301" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
@@ -9115,13 +9097,13 @@
         <v>368</v>
       </c>
       <c r="B302" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C302" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="D302" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
@@ -9129,13 +9111,13 @@
         <v>369</v>
       </c>
       <c r="B303" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C303" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="D303" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
@@ -9143,13 +9125,13 @@
         <v>370</v>
       </c>
       <c r="B304" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C304" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D304" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
@@ -9157,13 +9139,13 @@
         <v>371</v>
       </c>
       <c r="B305" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C305" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D305" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -9171,13 +9153,13 @@
         <v>372</v>
       </c>
       <c r="B306" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C306" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D306" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
@@ -9185,13 +9167,13 @@
         <v>373</v>
       </c>
       <c r="B307" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C307" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D307" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -9199,13 +9181,13 @@
         <v>374</v>
       </c>
       <c r="B308" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C308" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="D308" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
@@ -9213,13 +9195,13 @@
         <v>375</v>
       </c>
       <c r="B309" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C309" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D309" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
@@ -9227,13 +9209,13 @@
         <v>376</v>
       </c>
       <c r="B310" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C310" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D310" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
@@ -9241,13 +9223,13 @@
         <v>377</v>
       </c>
       <c r="B311" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C311" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D311" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
@@ -9255,13 +9237,13 @@
         <v>378</v>
       </c>
       <c r="B312" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C312" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D312" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
@@ -9269,13 +9251,13 @@
         <v>379</v>
       </c>
       <c r="B313" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C313" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D313" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
@@ -9283,13 +9265,13 @@
         <v>380</v>
       </c>
       <c r="B314" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C314" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D314" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -9297,13 +9279,13 @@
         <v>381</v>
       </c>
       <c r="B315" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C315" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D315" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
@@ -9311,13 +9293,13 @@
         <v>382</v>
       </c>
       <c r="B316" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C316" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D316" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
@@ -9325,13 +9307,13 @@
         <v>383</v>
       </c>
       <c r="B317" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C317" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D317" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
@@ -9339,13 +9321,13 @@
         <v>384</v>
       </c>
       <c r="B318" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C318" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D318" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
@@ -9353,13 +9335,13 @@
         <v>385</v>
       </c>
       <c r="B319" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C319" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D319" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
@@ -9367,13 +9349,13 @@
         <v>386</v>
       </c>
       <c r="B320" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C320" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D320" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
@@ -9381,13 +9363,13 @@
         <v>387</v>
       </c>
       <c r="B321" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C321" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="D321" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
@@ -9395,13 +9377,13 @@
         <v>388</v>
       </c>
       <c r="B322" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C322" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D322" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
@@ -9409,13 +9391,13 @@
         <v>389</v>
       </c>
       <c r="B323" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C323" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="D323" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
@@ -9423,13 +9405,13 @@
         <v>390</v>
       </c>
       <c r="B324" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C324" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D324" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
@@ -9437,13 +9419,13 @@
         <v>391</v>
       </c>
       <c r="B325" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C325" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="D325" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
@@ -9451,13 +9433,13 @@
         <v>392</v>
       </c>
       <c r="B326" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C326" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D326" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
@@ -9465,13 +9447,13 @@
         <v>393</v>
       </c>
       <c r="B327" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C327" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D327" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
@@ -9479,13 +9461,13 @@
         <v>394</v>
       </c>
       <c r="B328" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C328" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D328" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
@@ -9493,13 +9475,13 @@
         <v>395</v>
       </c>
       <c r="B329" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C329" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="D329" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
@@ -9507,13 +9489,13 @@
         <v>396</v>
       </c>
       <c r="B330" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C330" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="D330" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
@@ -9521,13 +9503,13 @@
         <v>397</v>
       </c>
       <c r="B331" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C331" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D331" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
@@ -9535,13 +9517,13 @@
         <v>398</v>
       </c>
       <c r="B332" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C332" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D332" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
@@ -9549,13 +9531,13 @@
         <v>399</v>
       </c>
       <c r="B333" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C333" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="D333" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
@@ -9563,13 +9545,13 @@
         <v>400</v>
       </c>
       <c r="B334" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C334" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D334" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
@@ -9577,13 +9559,13 @@
         <v>401</v>
       </c>
       <c r="B335" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C335" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="D335" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
@@ -9591,13 +9573,13 @@
         <v>402</v>
       </c>
       <c r="B336" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C336" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="D336" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
@@ -9605,13 +9587,13 @@
         <v>403</v>
       </c>
       <c r="B337" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C337" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="D337" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
@@ -9619,13 +9601,13 @@
         <v>404</v>
       </c>
       <c r="B338" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C338" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D338" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
@@ -9633,13 +9615,13 @@
         <v>405</v>
       </c>
       <c r="B339" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C339" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D339" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
@@ -9647,13 +9629,13 @@
         <v>406</v>
       </c>
       <c r="B340" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C340" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D340" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
@@ -9661,13 +9643,13 @@
         <v>407</v>
       </c>
       <c r="B341" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C341" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="D341" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
@@ -9675,13 +9657,13 @@
         <v>408</v>
       </c>
       <c r="B342" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C342" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="D342" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
@@ -9689,13 +9671,13 @@
         <v>409</v>
       </c>
       <c r="B343" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C343" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="D343" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
@@ -9703,13 +9685,13 @@
         <v>410</v>
       </c>
       <c r="B344" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C344" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="D344" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
@@ -9717,13 +9699,13 @@
         <v>411</v>
       </c>
       <c r="B345" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C345" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="D345" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
@@ -9731,13 +9713,13 @@
         <v>412</v>
       </c>
       <c r="B346" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C346" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="D346" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
@@ -9745,13 +9727,13 @@
         <v>413</v>
       </c>
       <c r="B347" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C347" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="D347" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
@@ -9759,13 +9741,13 @@
         <v>414</v>
       </c>
       <c r="B348" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C348" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="D348" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
@@ -9773,13 +9755,13 @@
         <v>415</v>
       </c>
       <c r="B349" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C349" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="D349" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
@@ -9787,13 +9769,13 @@
         <v>416</v>
       </c>
       <c r="B350" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="C350" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="D350" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
@@ -9801,13 +9783,13 @@
         <v>417</v>
       </c>
       <c r="B351" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C351" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D351" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
@@ -9815,13 +9797,13 @@
         <v>418</v>
       </c>
       <c r="B352" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C352" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D352" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
@@ -9829,13 +9811,13 @@
         <v>419</v>
       </c>
       <c r="B353" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C353" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D353" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
@@ -9843,13 +9825,13 @@
         <v>420</v>
       </c>
       <c r="B354" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C354" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="D354" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
@@ -9857,13 +9839,13 @@
         <v>421</v>
       </c>
       <c r="B355" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C355" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="D355" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
@@ -9871,13 +9853,13 @@
         <v>422</v>
       </c>
       <c r="B356" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C356" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="D356" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
@@ -9885,13 +9867,13 @@
         <v>423</v>
       </c>
       <c r="B357" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C357" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="D357" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
@@ -9899,13 +9881,13 @@
         <v>424</v>
       </c>
       <c r="B358" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C358" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="D358" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
@@ -9913,13 +9895,13 @@
         <v>425</v>
       </c>
       <c r="B359" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C359" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D359" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
@@ -9927,13 +9909,13 @@
         <v>426</v>
       </c>
       <c r="B360" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C360" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D360" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
@@ -9941,13 +9923,13 @@
         <v>427</v>
       </c>
       <c r="B361" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C361" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D361" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
@@ -9955,13 +9937,13 @@
         <v>428</v>
       </c>
       <c r="B362" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C362" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="D362" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
@@ -9969,13 +9951,13 @@
         <v>429</v>
       </c>
       <c r="B363" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C363" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="D363" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
@@ -9983,13 +9965,13 @@
         <v>430</v>
       </c>
       <c r="B364" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C364" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="D364" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
@@ -9997,13 +9979,13 @@
         <v>431</v>
       </c>
       <c r="B365" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C365" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="D365" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
@@ -10011,13 +9993,13 @@
         <v>432</v>
       </c>
       <c r="B366" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C366" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D366" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
@@ -10025,13 +10007,13 @@
         <v>433</v>
       </c>
       <c r="B367" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C367" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="D367" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
@@ -10039,13 +10021,13 @@
         <v>434</v>
       </c>
       <c r="B368" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C368" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="D368" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
@@ -10053,13 +10035,13 @@
         <v>435</v>
       </c>
       <c r="B369" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C369" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="D369" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
@@ -10067,13 +10049,13 @@
         <v>436</v>
       </c>
       <c r="B370" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C370" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="D370" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
@@ -10081,13 +10063,13 @@
         <v>437</v>
       </c>
       <c r="B371" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C371" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="D371" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
@@ -10095,13 +10077,13 @@
         <v>438</v>
       </c>
       <c r="B372" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C372" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D372" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
@@ -10109,13 +10091,13 @@
         <v>439</v>
       </c>
       <c r="B373" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C373" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D373" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
@@ -10123,13 +10105,13 @@
         <v>440</v>
       </c>
       <c r="B374" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C374" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="D374" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
@@ -10137,13 +10119,13 @@
         <v>441</v>
       </c>
       <c r="B375" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C375" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="D375" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
@@ -10151,13 +10133,13 @@
         <v>442</v>
       </c>
       <c r="B376" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C376" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D376" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
@@ -10165,13 +10147,13 @@
         <v>443</v>
       </c>
       <c r="B377" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C377" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="D377" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
@@ -10179,13 +10161,13 @@
         <v>444</v>
       </c>
       <c r="B378" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C378" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="D378" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
@@ -10193,13 +10175,13 @@
         <v>445</v>
       </c>
       <c r="B379" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C379" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="D379" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
@@ -10207,13 +10189,13 @@
         <v>446</v>
       </c>
       <c r="B380" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C380" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D380" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
@@ -10221,13 +10203,13 @@
         <v>447</v>
       </c>
       <c r="B381" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C381" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="D381" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
@@ -10235,13 +10217,13 @@
         <v>448</v>
       </c>
       <c r="B382" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C382" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="D382" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
@@ -10249,13 +10231,13 @@
         <v>449</v>
       </c>
       <c r="B383" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C383" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D383" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
@@ -10263,13 +10245,13 @@
         <v>450</v>
       </c>
       <c r="B384" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C384" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="D384" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
@@ -10277,13 +10259,13 @@
         <v>451</v>
       </c>
       <c r="B385" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C385" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="D385" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
@@ -10291,13 +10273,13 @@
         <v>452</v>
       </c>
       <c r="B386" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C386" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="D386" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
@@ -10305,13 +10287,13 @@
         <v>453</v>
       </c>
       <c r="B387" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C387" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="D387" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
@@ -10319,13 +10301,13 @@
         <v>454</v>
       </c>
       <c r="B388" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C388" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="D388" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
@@ -10333,13 +10315,13 @@
         <v>455</v>
       </c>
       <c r="B389" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C389" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="D389" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
@@ -10347,13 +10329,13 @@
         <v>456</v>
       </c>
       <c r="B390" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C390" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="D390" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
@@ -10361,13 +10343,13 @@
         <v>457</v>
       </c>
       <c r="B391" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C391" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="D391" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
@@ -10375,13 +10357,13 @@
         <v>458</v>
       </c>
       <c r="B392" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C392" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="D392" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
@@ -10389,13 +10371,13 @@
         <v>459</v>
       </c>
       <c r="B393" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C393" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D393" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
@@ -10403,13 +10385,13 @@
         <v>460</v>
       </c>
       <c r="B394" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C394" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="D394" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
@@ -10417,13 +10399,13 @@
         <v>461</v>
       </c>
       <c r="B395" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C395" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D395" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
@@ -10431,13 +10413,13 @@
         <v>462</v>
       </c>
       <c r="B396" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C396" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="D396" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
@@ -10445,13 +10427,13 @@
         <v>463</v>
       </c>
       <c r="B397" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C397" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D397" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
@@ -10459,13 +10441,13 @@
         <v>464</v>
       </c>
       <c r="B398" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C398" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="D398" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
@@ -10473,13 +10455,13 @@
         <v>465</v>
       </c>
       <c r="B399" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C399" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="D399" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
@@ -10487,13 +10469,13 @@
         <v>466</v>
       </c>
       <c r="B400" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C400" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D400" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
@@ -10501,13 +10483,13 @@
         <v>467</v>
       </c>
       <c r="B401" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C401" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="D401" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
@@ -10515,13 +10497,13 @@
         <v>468</v>
       </c>
       <c r="B402" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C402" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="D402" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
@@ -10529,13 +10511,13 @@
         <v>469</v>
       </c>
       <c r="B403" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C403" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="D403" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
@@ -10543,13 +10525,13 @@
         <v>470</v>
       </c>
       <c r="B404" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C404" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D404" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
@@ -10557,13 +10539,13 @@
         <v>471</v>
       </c>
       <c r="B405" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C405" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="D405" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
@@ -10571,13 +10553,13 @@
         <v>472</v>
       </c>
       <c r="B406" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C406" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="D406" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
@@ -10585,13 +10567,13 @@
         <v>473</v>
       </c>
       <c r="B407" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C407" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="D407" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
@@ -10599,13 +10581,13 @@
         <v>474</v>
       </c>
       <c r="B408" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C408" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="D408" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
@@ -10613,13 +10595,13 @@
         <v>475</v>
       </c>
       <c r="B409" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C409" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="D409" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
@@ -10627,13 +10609,13 @@
         <v>476</v>
       </c>
       <c r="B410" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C410" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="D410" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
@@ -10641,13 +10623,13 @@
         <v>477</v>
       </c>
       <c r="B411" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C411" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D411" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
@@ -10655,13 +10637,13 @@
         <v>478</v>
       </c>
       <c r="B412" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C412" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="D412" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
@@ -10669,13 +10651,13 @@
         <v>479</v>
       </c>
       <c r="B413" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C413" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="D413" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
@@ -10683,13 +10665,13 @@
         <v>480</v>
       </c>
       <c r="B414" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C414" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D414" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
@@ -10697,13 +10679,13 @@
         <v>481</v>
       </c>
       <c r="B415" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C415" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D415" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
@@ -10711,13 +10693,13 @@
         <v>482</v>
       </c>
       <c r="B416" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C416" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="D416" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
@@ -10725,13 +10707,13 @@
         <v>483</v>
       </c>
       <c r="B417" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C417" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="D417" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
@@ -10739,13 +10721,13 @@
         <v>484</v>
       </c>
       <c r="B418" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C418" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="D418" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.3">
@@ -10753,13 +10735,13 @@
         <v>485</v>
       </c>
       <c r="B419" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C419" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D419" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.3">
@@ -10767,13 +10749,13 @@
         <v>486</v>
       </c>
       <c r="B420" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C420" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="D420" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.3">
@@ -10781,13 +10763,13 @@
         <v>487</v>
       </c>
       <c r="B421" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C421" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="D421" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.3">
@@ -10795,13 +10777,13 @@
         <v>488</v>
       </c>
       <c r="B422" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C422" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="D422" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
@@ -10809,13 +10791,13 @@
         <v>489</v>
       </c>
       <c r="B423" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C423" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="D423" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
@@ -10823,13 +10805,13 @@
         <v>490</v>
       </c>
       <c r="B424" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C424" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="D424" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.3">
@@ -10837,13 +10819,13 @@
         <v>491</v>
       </c>
       <c r="B425" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C425" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D425" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
@@ -10851,13 +10833,13 @@
         <v>492</v>
       </c>
       <c r="B426" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C426" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D426" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
@@ -10865,13 +10847,13 @@
         <v>493</v>
       </c>
       <c r="B427" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C427" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="D427" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
@@ -10879,13 +10861,13 @@
         <v>494</v>
       </c>
       <c r="B428" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C428" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="D428" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
@@ -10893,13 +10875,13 @@
         <v>495</v>
       </c>
       <c r="B429" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C429" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="D429" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
@@ -10907,13 +10889,13 @@
         <v>496</v>
       </c>
       <c r="B430" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C430" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D430" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
@@ -10921,13 +10903,13 @@
         <v>497</v>
       </c>
       <c r="B431" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C431" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D431" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
@@ -10935,13 +10917,13 @@
         <v>498</v>
       </c>
       <c r="B432" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C432" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D432" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.3">
@@ -10949,13 +10931,13 @@
         <v>499</v>
       </c>
       <c r="B433" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C433" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="D433" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.3">
@@ -10963,13 +10945,13 @@
         <v>500</v>
       </c>
       <c r="B434" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C434" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D434" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.3">
@@ -10977,13 +10959,13 @@
         <v>501</v>
       </c>
       <c r="B435" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C435" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="D435" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
@@ -10991,13 +10973,13 @@
         <v>502</v>
       </c>
       <c r="B436" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C436" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="D436" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
@@ -11005,13 +10987,13 @@
         <v>503</v>
       </c>
       <c r="B437" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C437" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D437" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.3">
@@ -11019,13 +11001,13 @@
         <v>504</v>
       </c>
       <c r="B438" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C438" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D438" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.3">
@@ -11033,13 +11015,13 @@
         <v>505</v>
       </c>
       <c r="B439" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C439" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D439" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.3">
@@ -11047,13 +11029,13 @@
         <v>506</v>
       </c>
       <c r="B440" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C440" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D440" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.3">
@@ -11061,13 +11043,13 @@
         <v>507</v>
       </c>
       <c r="B441" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C441" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D441" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
@@ -11075,13 +11057,13 @@
         <v>508</v>
       </c>
       <c r="B442" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="C442" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="D442" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
@@ -11089,13 +11071,13 @@
         <v>509</v>
       </c>
       <c r="B443" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C443" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="D443" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
@@ -11103,13 +11085,13 @@
         <v>510</v>
       </c>
       <c r="B444" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C444" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="D444" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
@@ -11117,13 +11099,13 @@
         <v>511</v>
       </c>
       <c r="B445" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C445" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="D445" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.3">
@@ -11131,13 +11113,13 @@
         <v>512</v>
       </c>
       <c r="B446" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C446" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="D446" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.3">
@@ -11145,13 +11127,13 @@
         <v>513</v>
       </c>
       <c r="B447" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C447" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="D447" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.3">
@@ -11159,13 +11141,13 @@
         <v>514</v>
       </c>
       <c r="B448" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C448" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="D448" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.3">
@@ -11173,13 +11155,13 @@
         <v>515</v>
       </c>
       <c r="B449" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C449" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="D449" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.3">
@@ -11187,13 +11169,13 @@
         <v>516</v>
       </c>
       <c r="B450" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C450" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="D450" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
@@ -11201,13 +11183,13 @@
         <v>517</v>
       </c>
       <c r="B451" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C451" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="D451" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.3">
@@ -11215,13 +11197,13 @@
         <v>518</v>
       </c>
       <c r="B452" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C452" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="D452" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
@@ -11229,13 +11211,13 @@
         <v>519</v>
       </c>
       <c r="B453" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C453" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="D453" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.3">
@@ -11243,13 +11225,13 @@
         <v>520</v>
       </c>
       <c r="B454" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C454" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="D454" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
@@ -11257,13 +11239,13 @@
         <v>521</v>
       </c>
       <c r="B455" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C455" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="D455" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
@@ -11271,13 +11253,13 @@
         <v>522</v>
       </c>
       <c r="B456" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C456" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="D456" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
@@ -11285,13 +11267,13 @@
         <v>523</v>
       </c>
       <c r="B457" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C457" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="D457" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.3">
@@ -11299,13 +11281,13 @@
         <v>524</v>
       </c>
       <c r="B458" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C458" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="D458" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.3">
@@ -11313,13 +11295,13 @@
         <v>525</v>
       </c>
       <c r="B459" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="C459" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="D459" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
@@ -11327,13 +11309,13 @@
         <v>526</v>
       </c>
       <c r="B460" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="C460" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="D460" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
@@ -11341,13 +11323,13 @@
         <v>527</v>
       </c>
       <c r="B461" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C461" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="D461" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
@@ -11355,13 +11337,13 @@
         <v>528</v>
       </c>
       <c r="B462" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C462" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="D462" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.3">
@@ -11369,13 +11351,13 @@
         <v>529</v>
       </c>
       <c r="B463" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C463" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="D463" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.3">
@@ -11383,13 +11365,13 @@
         <v>530</v>
       </c>
       <c r="B464" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C464" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="D464" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.3">
@@ -11397,13 +11379,13 @@
         <v>531</v>
       </c>
       <c r="B465" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C465" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D465" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.3">
@@ -11411,13 +11393,13 @@
         <v>532</v>
       </c>
       <c r="B466" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C466" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D466" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.3">
@@ -11425,13 +11407,13 @@
         <v>533</v>
       </c>
       <c r="B467" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C467" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D467" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.3">
@@ -11439,13 +11421,13 @@
         <v>534</v>
       </c>
       <c r="B468" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C468" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="D468" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.3">
@@ -11453,13 +11435,13 @@
         <v>535</v>
       </c>
       <c r="B469" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C469" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D469" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.3">
@@ -11467,13 +11449,13 @@
         <v>536</v>
       </c>
       <c r="B470" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C470" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="D470" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.3">
@@ -11481,13 +11463,13 @@
         <v>537</v>
       </c>
       <c r="B471" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C471" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D471" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.3">
@@ -11495,13 +11477,13 @@
         <v>538</v>
       </c>
       <c r="B472" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="C472" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D472" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.3">
@@ -11509,13 +11491,13 @@
         <v>539</v>
       </c>
       <c r="B473" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="C473" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D473" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.3">
@@ -11523,13 +11505,13 @@
         <v>540</v>
       </c>
       <c r="B474" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="C474" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="D474" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.3">
@@ -11537,13 +11519,13 @@
         <v>541</v>
       </c>
       <c r="B475" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C475" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="D475" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.3">
@@ -11551,13 +11533,13 @@
         <v>542</v>
       </c>
       <c r="B476" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C476" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D476" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.3">
@@ -11565,13 +11547,13 @@
         <v>543</v>
       </c>
       <c r="B477" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C477" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D477" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.3">
@@ -11579,13 +11561,13 @@
         <v>544</v>
       </c>
       <c r="B478" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C478" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D478" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.3">
@@ -11593,13 +11575,13 @@
         <v>545</v>
       </c>
       <c r="B479" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="C479" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D479" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.3">
@@ -11607,13 +11589,13 @@
         <v>546</v>
       </c>
       <c r="B480" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C480" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D480" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.3">
@@ -11621,13 +11603,13 @@
         <v>547</v>
       </c>
       <c r="B481" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="C481" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D481" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.3">
@@ -11635,13 +11617,13 @@
         <v>548</v>
       </c>
       <c r="B482" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C482" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D482" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.3">
@@ -11649,13 +11631,13 @@
         <v>549</v>
       </c>
       <c r="B483" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="C483" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D483" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.3">
@@ -11663,13 +11645,13 @@
         <v>550</v>
       </c>
       <c r="B484" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="C484" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D484" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.3">
@@ -11677,13 +11659,13 @@
         <v>551</v>
       </c>
       <c r="B485" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="C485" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D485" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.3">
@@ -11691,13 +11673,13 @@
         <v>552</v>
       </c>
       <c r="B486" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C486" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D486" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.3">
@@ -11705,13 +11687,13 @@
         <v>553</v>
       </c>
       <c r="B487" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C487" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D487" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.3">
@@ -11719,13 +11701,13 @@
         <v>554</v>
       </c>
       <c r="B488" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C488" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="D488" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.3">
@@ -11733,13 +11715,13 @@
         <v>555</v>
       </c>
       <c r="B489" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="C489" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D489" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.3">
@@ -11747,13 +11729,13 @@
         <v>556</v>
       </c>
       <c r="B490" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="C490" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D490" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.3">
@@ -11761,13 +11743,13 @@
         <v>557</v>
       </c>
       <c r="B491" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C491" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="D491" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.3">
@@ -11775,13 +11757,13 @@
         <v>558</v>
       </c>
       <c r="B492" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C492" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="D492" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.3">
@@ -11789,13 +11771,13 @@
         <v>559</v>
       </c>
       <c r="B493" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="C493" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="D493" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.3">
@@ -11803,13 +11785,13 @@
         <v>560</v>
       </c>
       <c r="B494" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="C494" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D494" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.3">
@@ -11817,13 +11799,13 @@
         <v>561</v>
       </c>
       <c r="B495" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C495" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D495" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.3">
@@ -11831,45 +11813,17 @@
         <v>562</v>
       </c>
       <c r="B496" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="C496" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="D496" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A497" t="s">
-        <v>563</v>
-      </c>
-      <c r="B497" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1417</v>
-      </c>
-      <c r="D497" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A498" t="s">
-        <v>564</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C498" t="s">
-        <v>1419</v>
-      </c>
-      <c r="D498" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D498" xr:uid="{5405E5E4-8AD8-41E7-B4EE-E3800A1407B4}"/>
+  <autoFilter ref="A1:D496" xr:uid="{5405E5E4-8AD8-41E7-B4EE-E3800A1407B4}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>